--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,16 +8,16 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio_Guia" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Documentos_Entradas" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Matriz_RV32I" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Escenarios_Prueba" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Cobertura_Modulos" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="MMIO_Interrupts_Traps" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="Listas" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Pipeline_5Etapas" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Hazards_Forwarding" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="Inicio_Guia" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Documentos_Entradas" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Matriz_RV32I" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Escenarios_Prueba" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Cobertura_Modulos" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="MMIO_Interrupts_Traps" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Listas" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Pipeline_5Etapas" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Hazards_Forwarding" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -2011,78 +2011,82 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
-    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2125,38 +2129,27 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <name val="Lohit Devanagari"/>
-        <charset val="1"/>
-        <family val="2"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F4E78"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Calibri"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <color rgb="FFFFFFFF"/>
-        <u val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="General"/>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFFF"/>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
-      <border diagonalUp="false" diagonalDown="false">
-        <left/>
-        <right/>
-        <top/>
-        <bottom/>
-        <diagonal/>
-      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -2222,7 +2215,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2234,19 +2227,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
@@ -2258,7 +2249,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2287,20 +2278,37 @@
             <a:solidFill>
               <a:srgbClr val="156082"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="12600">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -2352,11 +2360,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="78018825"/>
-        <c:axId val="76642028"/>
+        <c:axId val="52399148"/>
+        <c:axId val="64857148"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="78018825"/>
+        <c:axId val="52399148"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2372,7 +2380,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2389,24 +2397,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76642028"/>
+        <c:crossAx val="64857148"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76642028"/>
+        <c:axId val="64857148"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2439,24 +2449,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78018825"/>
+        <c:crossAx val="52399148"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2466,7 +2478,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2475,10 +2487,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Calibri"/>
             </a:defRPr>
@@ -2503,7 +2516,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2515,19 +2528,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-ES" sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
@@ -2539,7 +2550,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2568,20 +2579,37 @@
             <a:solidFill>
               <a:srgbClr val="156082"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln w="12600">
               <a:noFill/>
             </a:ln>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="0%" sourceLinked="1"/>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="0"/>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -2634,7 +2662,7 @@
             <c:numRef>
               <c:f>Dashboard!$E$11:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
@@ -2681,11 +2709,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="97996195"/>
-        <c:axId val="32732961"/>
+        <c:axId val="83459522"/>
+        <c:axId val="58780389"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97996195"/>
+        <c:axId val="83459522"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2701,7 +2729,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2718,24 +2746,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32732961"/>
+        <c:crossAx val="58780389"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32732961"/>
+        <c:axId val="58780389"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2768,24 +2798,26 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97996195"/>
+        <c:crossAx val="83459522"/>
         <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2795,7 +2827,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2804,10 +2836,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Calibri"/>
             </a:defRPr>
@@ -2836,20 +2869,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1440</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>263520</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1309320</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>10440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6791760</xdr:colOff>
+      <xdr:colOff>6754320</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>158040</xdr:rowOff>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Imagen 1" descr=""/>
+        <xdr:cNvPr id="1" name="Imagen 1"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2858,13 +2891,14 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2007720" y="9258120"/>
-          <a:ext cx="18124560" cy="3299400"/>
+          <a:off x="1969200" y="9150480"/>
+          <a:ext cx="18111960" cy="3266640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -2873,20 +2907,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1335240</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>51840</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>222480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6956280</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>24480</xdr:rowOff>
+      <xdr:colOff>7017480</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>156240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Imagen 2" descr=""/>
+        <xdr:cNvPr id="2" name="Imagen 2"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2895,13 +2929,14 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1995480" y="5461920"/>
-          <a:ext cx="18301320" cy="3366720"/>
+          <a:off x="2056680" y="5150160"/>
+          <a:ext cx="18287640" cy="3366360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -2910,20 +2945,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1334880</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>436320</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>14400</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>41040</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6926760</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>396360</xdr:rowOff>
+      <xdr:colOff>6950880</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>176760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 3" descr=""/>
+        <xdr:cNvPr id="3" name="Imagen 3"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2932,13 +2967,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1995120" y="12835800"/>
-          <a:ext cx="18272160" cy="3003480"/>
+          <a:off x="2019240" y="13147920"/>
+          <a:ext cx="18258480" cy="3003480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>24120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6687360</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>159480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2028240" y="16570440"/>
+          <a:ext cx="17985960" cy="3051000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -2959,18 +3033,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>758160</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>190440</xdr:rowOff>
+      <xdr:colOff>757800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>131760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart"/>
+        <xdr:cNvPr id="5" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9530640" y="380880"/>
-        <a:ext cx="4911120" cy="3047760"/>
+        <a:off x="9521280" y="380880"/>
+        <a:ext cx="4906800" cy="3047760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2984,23 +3058,23 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>114120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>758160</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:colOff>757800</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>6840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart"/>
+        <xdr:cNvPr id="6" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9530640" y="3619440"/>
-        <a:ext cx="4911120" cy="3999960"/>
+        <a:off x="9521280" y="3619440"/>
+        <a:ext cx="4906800" cy="3999960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3031,260 +3105,366 @@
 </table>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="129.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="178.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="0" width="0.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="0.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="129.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="178.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="0.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="0.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3293,372 +3473,372 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="31.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="33.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="31.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="33.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="L2" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="L3" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="L4" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="L5" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="L6" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="L7" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="L8" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="3" t="s">
         <v>102</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3667,396 +3847,396 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="64.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="99.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="0.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="99.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="7.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="0.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="s">
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="s">
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F11">
@@ -4077,14 +4257,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F11" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F11" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4093,1695 +4273,1695 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="15" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>110111</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>10111</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>1101111</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1100111</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
+      <c r="E5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="K6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L7" s="2" t="s">
+      <c r="K7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="5"/>
+      <c r="G8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="2" t="s">
+      <c r="K8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="2" t="s">
+      <c r="F9" s="5"/>
+      <c r="G9" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="K9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="2" t="s">
+      <c r="F10" s="5"/>
+      <c r="G10" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="K10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>1100011</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E11" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="2" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="K11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="2" t="s">
+      <c r="E12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L12" s="2" t="s">
+      <c r="K12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="M12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="E13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="2" t="s">
+      <c r="F13" s="5"/>
+      <c r="G13" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="M13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="2" t="s">
+      <c r="F14" s="5"/>
+      <c r="G14" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="M14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="2" t="s">
+      <c r="F15" s="5"/>
+      <c r="G15" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L15" s="2" t="s">
+      <c r="K15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="M15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="2" t="s">
+      <c r="F16" s="5"/>
+      <c r="G16" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="J16" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L16" s="2" t="s">
+      <c r="K16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="M16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>100011</v>
       </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="2" t="s">
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="K17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="M17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>100011</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="2" t="s">
+      <c r="F18" s="5"/>
+      <c r="G18" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="J18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L18" s="2" t="s">
+      <c r="K18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="M18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>100011</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="E19" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="2" t="s">
+      <c r="F19" s="5"/>
+      <c r="G19" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L19" s="2" t="s">
+      <c r="K19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="M19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="2" t="s">
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J20" s="2" t="s">
+      <c r="J20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L20" s="2" t="s">
+      <c r="K20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="M20" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="2" t="s">
+      <c r="F21" s="5"/>
+      <c r="G21" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="J21" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L21" s="2" t="s">
+      <c r="K21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="M21" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="2" t="s">
+      <c r="F22" s="5"/>
+      <c r="G22" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="H22" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I22" s="2" t="s">
+      <c r="I22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J22" s="2" t="s">
+      <c r="J22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L22" s="2" t="s">
+      <c r="K22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="M22" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="E23" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="2" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="H23" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="I23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="J23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L23" s="2" t="s">
+      <c r="K23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="M23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="2" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="J24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="K24" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="M24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="E25" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="2" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="I25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="J25" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L25" s="2" t="s">
+      <c r="K25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="M25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="I26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="J26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K26" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="K26" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="M26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="E27" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="2" t="s">
+      <c r="F27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="I27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="J27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="K27" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="M27" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="6" t="n">
         <v>10011</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="I28" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="J28" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K28" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L28" s="2" t="s">
+      <c r="K28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="M28" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="E29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="H29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="I29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L29" s="2" t="s">
+      <c r="K29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="M29" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="n">
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="I30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="J30" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L30" s="2" t="s">
+      <c r="K30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="M30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="E31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H31" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="I31" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K31" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L31" s="2" t="s">
+      <c r="K31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="M31" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="F32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="J32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L32" s="2" t="s">
+      <c r="K32" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="M32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E33" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="F33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="s">
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="I33" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="J33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L33" s="2" t="s">
+      <c r="K33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="M33" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="E34" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="I34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="J34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L34" s="2" t="s">
+      <c r="K34" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="M34" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="E35" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
+      <c r="F35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="I35" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="J35" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L35" s="2" t="s">
+      <c r="K35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="M35" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N35" s="2"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="E36" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="6" t="n">
         <v>100000</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="I36" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="J36" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L36" s="2" t="s">
+      <c r="K36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="M36" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="N36" s="3"/>
+    </row>
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="E37" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="F37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H37" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="I37" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="J37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L37" s="2" t="s">
+      <c r="K37" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="M37" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="6" t="n">
         <v>110011</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="E38" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="2" t="s">
+      <c r="F38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H38" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I38" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L38" s="2" t="s">
+      <c r="K38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="M38" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="N38" s="3"/>
+    </row>
+    <row r="39" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="6" t="n">
         <v>1111</v>
       </c>
-      <c r="E39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="2" t="s">
+      <c r="E39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H39" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="I39" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="J39" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L39" s="2" t="s">
+      <c r="K39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="M39" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="N39" s="2"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="6" t="n">
         <v>1110011</v>
       </c>
-      <c r="E40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="2" t="s">
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I40" s="2" t="s">
+      <c r="I40" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J40" s="2" t="s">
+      <c r="J40" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L40" s="2" t="s">
+      <c r="K40" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="M40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="6" t="n">
         <v>1110011</v>
       </c>
-      <c r="E41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="7" t="n">
+      <c r="E41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="H41" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="K41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="M41" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N41" s="2"/>
+      <c r="N41" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="K2:K41">
@@ -5802,18 +5982,18 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K41" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K41" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M41" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M41" type="list">
       <formula1>Listas!$B$2:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5822,810 +6002,816 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M63"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="72.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="101.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="26.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="72.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="101.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="26.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="11" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L3" s="11"/>
-      <c r="M3" s="12"/>
-    </row>
-    <row r="4" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="L3" s="12"/>
+      <c r="M3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="J4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12"/>
-    </row>
-    <row r="5" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="L4" s="12"/>
+      <c r="M4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="J5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12"/>
-    </row>
-    <row r="6" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="L5" s="12"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="J6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L6" s="11"/>
-      <c r="M6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="L6" s="12"/>
+      <c r="M6" s="13"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="J7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L7" s="11"/>
-      <c r="M7" s="12"/>
-    </row>
-    <row r="8" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="L7" s="12"/>
+      <c r="M7" s="13"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="J8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L8" s="11"/>
-      <c r="M8" s="12"/>
-    </row>
-    <row r="9" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="L8" s="12"/>
+      <c r="M8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="2" t="s">
+      <c r="J9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L9" s="11"/>
-      <c r="M9" s="12"/>
-    </row>
-    <row r="10" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="L9" s="12"/>
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="J10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L10" s="11"/>
-      <c r="M10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="L10" s="12"/>
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="2" t="s">
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-    </row>
-    <row r="12" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="L11" s="12"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="2" t="s">
+      <c r="J12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12"/>
-    </row>
-    <row r="13" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="L12" s="12"/>
+      <c r="M12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L13" s="11"/>
-      <c r="M13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" s="2" t="s">
+      <c r="J14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L14" s="11"/>
-      <c r="M14" s="12"/>
-    </row>
-    <row r="15" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="L14" s="12"/>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="I15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="J15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L15" s="11"/>
-      <c r="M15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="L15" s="12"/>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="J16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L16" s="11"/>
-      <c r="M16" s="12"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="L16" s="12"/>
+      <c r="M16" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="I17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K17" s="2" t="s">
+      <c r="J17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="11"/>
-      <c r="M17" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="L17" s="12"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="I18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="J18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="11"/>
-      <c r="M18" s="12"/>
-    </row>
-    <row r="19" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="L18" s="12"/>
+      <c r="M18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="J19" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L19" s="11"/>
-      <c r="M19" s="12"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="L19" s="12"/>
+      <c r="M19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="I20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K20" s="2" t="s">
+      <c r="J20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L20" s="11"/>
-      <c r="M20" s="12"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="L20" s="12"/>
+      <c r="M20" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="103.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
+    <row r="26" customFormat="false" ht="102.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="14" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0"/>
+    </row>
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="148.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="13" t="s">
+    <row r="41" customFormat="false" ht="147.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="14" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="136.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="13" t="s">
+    <row r="53" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="14" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="125.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="13" t="s">
+    <row r="63" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="14" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6648,26 +6834,26 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H20" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H20" type="list">
       <formula1>Listas!$C$2:$C$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I20" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I20" type="list">
       <formula1>Listas!$D$2:$D$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K20" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K20" type="list">
       <formula1>Listas!$B$2:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6677,422 +6863,422 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="56.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F14">
@@ -7121,20 +7307,20 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{85904ED0-FBB8-46CC-8819-54FD1C19A1D1}</x14:id>
+          <x14:id>{904C8EBB-B655-4444-83BD-584A58B0C0B5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F14" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F14" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7143,7 +7329,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{85904ED0-FBB8-46CC-8819-54FD1C19A1D1}">
+          <x14:cfRule type="dataBar" id="{904C8EBB-B655-4444-83BD-584A58B0C0B5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7160,608 +7346,608 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="5.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="5.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="5.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="9" style="1" width="10.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Matriz_RV32I!B2:B100)</f>
         <v>40</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <f aca="false">IFERROR(COUNTIF(Cobertura_Modulos!F2:F100,"Completado")/COUNTIF(Cobertura_Modulos!F2:F100,"&lt;&gt;N/A"),0)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF(Hazards_Forwarding!L2:L100,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B9" s="2" t="n">
-        <f aca="false">COUNTIF(Escenarios_Prueba!J2:J100,"Completado")</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="B9" s="3" t="n">
+        <f aca="false">COUNTIF(Escenarios_Prueba!J2:J106,"Completado")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="3" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B11" s="2" t="n">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"No iniciado")</f>
         <v>40</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D11,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="2" t="str">
+      <c r="F11" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D11,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D11,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/4</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"En progreso")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D12,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="str">
+      <c r="F12" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D12,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D12,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/2</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Bloqueado")</f>
         <v>0</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D13,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="2" t="str">
+      <c r="F13" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D13,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D13,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/2</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D14,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="str">
+      <c r="F14" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D14,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D14,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/1</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"N/A")</f>
         <v>0</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D15,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="2" t="str">
+      <c r="F15" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D15,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D15,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/1</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="2" t="str">
+      <c r="F16" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D16,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/1</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Documentos_Entradas!D2:D100,"Sí")</f>
         <v>10</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="2" t="str">
+      <c r="F17" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D17,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/3</v>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="4" t="n">
         <f aca="false">COUNTIFS(Documentos_Entradas!D2:D100,"Sí",Documentos_Entradas!I2:I100,"Completo")</f>
         <v>0</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="2" t="str">
+      <c r="F18" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D18,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/4</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B19" s="3" t="n">
         <f aca="false">COUNTA(MMIO_Interrupts_Traps!A2:A100)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="2" t="str">
+      <c r="F19" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D19,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/4</v>
       </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(MMIO_Interrupts_Traps!J2:J100,"Completado")</f>
         <v>0</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="2" t="str">
+      <c r="F20" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D20,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/3</v>
       </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B21" s="15" t="n">
         <f aca="false">IFERROR(B20/B19,0)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E21" s="14" t="n">
+      <c r="E21" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D21,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="2" t="str">
+      <c r="F21" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D21,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D21,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/2</v>
       </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="2" t="str">
+      <c r="F22" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D22,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/2</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="15" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D23,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="2" t="str">
+      <c r="F23" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D23,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D23,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0/2</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7776,14 +7962,14 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D5384B81-9AAB-4BF6-8DA9-F1E65060D730}</x14:id>
+          <x14:id>{6DC2ACFC-46D7-4A79-8892-582C30E3B6B1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7793,7 +7979,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D5384B81-9AAB-4BF6-8DA9-F1E65060D730}">
+          <x14:cfRule type="dataBar" id="{6DC2ACFC-46D7-4A79-8892-582C30E3B6B1}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7810,400 +7996,400 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="55.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="30.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="12" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="14" t="n">
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="15" t="n">
         <f aca="false">IF(G2=0,0,H2/G2)</f>
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="J2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="14" t="n">
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="15" t="n">
         <f aca="false">IF(G3=0,0,H3/G3)</f>
         <v>0</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="J3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="14" t="n">
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="n">
         <f aca="false">IF(G4=0,0,H4/G4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="J4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="14" t="n">
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="15" t="n">
         <f aca="false">IF(G5=0,0,H5/G5)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="J5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="14" t="n">
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="15" t="n">
         <f aca="false">IF(G6=0,0,H6/G6)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="J6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="14" t="n">
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="n">
         <f aca="false">IF(G7=0,0,H7/G7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="J7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="14" t="n">
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="n">
         <f aca="false">IF(G8=0,0,H8/G8)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="J8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="14" t="n">
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="n">
         <f aca="false">IF(G9=0,0,H9/G9)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="J9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="14" t="n">
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="n">
         <f aca="false">IF(G10=0,0,H10/G10)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="J10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="14" t="n">
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="15" t="n">
         <f aca="false">IF(G11=0,0,H11/G11)</f>
         <v>0</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="2"/>
+      <c r="J11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="K11" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J11">
@@ -8232,20 +8418,20 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{93BE3879-89A7-49FE-9A4E-254012D8FBAA}</x14:id>
+          <x14:id>{BDFDABC0-B840-44F9-8AED-17A2D0AAC8E3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J11" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J11" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8257,7 +8443,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{93BE3879-89A7-49FE-9A4E-254012D8FBAA}">
+          <x14:cfRule type="dataBar" id="{BDFDABC0-B840-44F9-8AED-17A2D0AAC8E3}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8274,115 +8460,115 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="22.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="22.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8391,424 +8577,424 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="77.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="108.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="62.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="110.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="43.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="69.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="30.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="0" width="10.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="77.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="108.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="110.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="69.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="L1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="I4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="I5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="I6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="I7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="I8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="I9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="I10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="I11" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
+      <c r="J12" s="3"/>
+      <c r="K12" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Inicio_Guia" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Documentos_Entradas" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Matriz_RV32I" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Escenarios_Prueba" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Cobertura_Modulos" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="MMIO_Interrupts_Traps" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Listas" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Pipeline_5Etapas" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Hazards_Forwarding" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Inicio_Guia" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Documentos_Entradas" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Matriz_RV32I" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Escenarios_Prueba" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Cobertura_Modulos" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="MMIO_Interrupts_Traps" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="Listas" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="Pipeline_5Etapas" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="Hazards_Forwarding" sheetId="10" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="602">
   <si>
     <t xml:space="preserve">Plantilla de verificación RV32I para core pipeline de 5 etapas con IF de 2 ciclos (BRAM síncrona)</t>
   </si>
@@ -1138,6 +1138,31 @@
     jal x0, done</t>
   </si>
   <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    addi x1, x0, 5
+    addi x2, x0, 5
+    beq  x1, x2, target
+    addi x10, x0, 0x0A
+    addi x11, x0, 0x0B
+    addi x12, x0, 0x0C
+    addi x13, x0, 0x0D
+    addi x14, x0, 0x0E
+target:
+    addi x20, x0, 0x1A
+    addi x21, x0, 0x1B
+    addi x22, x0, 0x1C
+    addi x23, x0, 0x1D
+    addi x24, x0, 0x1E
+done:
+    jal x0, done
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WB → OK</t>
+  </si>
+  <si>
     <t xml:space="preserve">Descripción</t>
   </si>
   <si>
@@ -1156,6 +1181,9 @@
     <t xml:space="preserve">Fetch, PC, reset vector, redirect</t>
   </si>
   <si>
+    <t xml:space="preserve">Completado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Registro de pipeline y flush/hold</t>
   </si>
   <si>
@@ -1274,9 +1302,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bloqueado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completado</t>
   </si>
   <si>
     <t xml:space="preserve">Docs</t>
@@ -2011,7 +2036,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2072,21 +2097,25 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Excel Built-in Explanatory Text" xfId="20"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3" customBuiltin="false"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6" customBuiltin="false"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4" customBuiltin="false"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7" customBuiltin="false"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
+    <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="2">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2120,36 +2149,6 @@
         <charset val="1"/>
         <family val="2"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Lohit Devanagari"/>
-        <charset val="1"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F4E78"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <colors>
@@ -2215,7 +2214,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2227,17 +2226,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="es-ES" sz="1800" b="1" u="none" strike="noStrike">
+              <a:rPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
@@ -2249,7 +2250,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2284,31 +2285,14 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
+            <c:numFmt formatCode="General" sourceLinked="1"/>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -2360,11 +2344,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="52399148"/>
-        <c:axId val="64857148"/>
+        <c:axId val="8450327"/>
+        <c:axId val="57998876"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="52399148"/>
+        <c:axId val="8450327"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2380,7 +2364,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2397,26 +2381,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64857148"/>
+        <c:crossAx val="57998876"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64857148"/>
+        <c:axId val="57998876"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2449,26 +2431,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52399148"/>
+        <c:crossAx val="8450327"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2478,7 +2458,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2487,11 +2467,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Calibri"/>
             </a:defRPr>
@@ -2516,7 +2495,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2528,17 +2507,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="es-ES" sz="1800" b="1" u="none" strike="noStrike">
+              <a:rPr b="1" lang="es-ES" sz="1800" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:rPr>
@@ -2550,7 +2531,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2585,31 +2566,14 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
+            <c:numFmt formatCode="0%" sourceLinked="1"/>
             <c:dLblPos val="outEnd"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
             <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -2662,13 +2626,13 @@
             <c:numRef>
               <c:f>Dashboard!$E$11:$E$23</c:f>
               <c:numCache>
-                <c:formatCode>0%</c:formatCode>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2709,11 +2673,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83459522"/>
-        <c:axId val="58780389"/>
+        <c:axId val="84834643"/>
+        <c:axId val="60193167"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83459522"/>
+        <c:axId val="84834643"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2729,7 +2693,7 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2746,26 +2710,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58780389"/>
+        <c:crossAx val="60193167"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58780389"/>
+        <c:axId val="60193167"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2798,26 +2760,24 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:uFillTx/>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83459522"/>
+        <c:crossAx val="84834643"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
         </a:solidFill>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2827,7 +2787,7 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </c:spPr>
@@ -2836,11 +2796,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr lang="es-ES" sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" lang="es-ES" sz="1000" spc="-1" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
-              <a:uFillTx/>
               <a:latin typeface="Calibri"/>
               <a:ea typeface="Calibri"/>
             </a:defRPr>
@@ -2876,13 +2835,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6754320</xdr:colOff>
+      <xdr:colOff>6753600</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>72000</xdr:rowOff>
+      <xdr:rowOff>71280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Imagen 1"/>
+        <xdr:cNvPr id="0" name="Imagen 1" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2891,14 +2850,13 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1969200" y="9150480"/>
-          <a:ext cx="18111960" cy="3266640"/>
+          <a:off x="1969560" y="9150480"/>
+          <a:ext cx="18123840" cy="3265560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -2914,13 +2872,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>7017480</xdr:colOff>
+      <xdr:colOff>7016760</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>156240</xdr:rowOff>
+      <xdr:rowOff>155520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 2"/>
+        <xdr:cNvPr id="1" name="Imagen 2" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2929,14 +2887,13 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2056680" y="5150160"/>
-          <a:ext cx="18287640" cy="3366360"/>
+          <a:off x="2058120" y="5149800"/>
+          <a:ext cx="18298440" cy="3366000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -2952,13 +2909,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6950880</xdr:colOff>
+      <xdr:colOff>6950160</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>176760</xdr:rowOff>
+      <xdr:rowOff>176040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 3"/>
+        <xdr:cNvPr id="2" name="Imagen 3" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2967,36 +2924,35 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2019240" y="13147920"/>
-          <a:ext cx="18258480" cy="3003480"/>
+          <a:off x="2020680" y="13147920"/>
+          <a:ext cx="18269280" cy="3002760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>23400</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>24120</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1321200</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114840</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6687360</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>159480</xdr:rowOff>
+      <xdr:colOff>6945480</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>29520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 1"/>
+        <xdr:cNvPr id="3" name="Imagen 4" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3005,14 +2961,50 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2028240" y="16570440"/>
-          <a:ext cx="17985960" cy="3051000"/>
+          <a:off x="1981440" y="16470360"/>
+          <a:ext cx="18303840" cy="3686040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>6892200</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>58320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 5" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2006280" y="20805120"/>
+          <a:ext cx="18225720" cy="4129920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
           <a:noFill/>
         </a:ln>
       </xdr:spPr>
@@ -3033,9 +3025,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>757800</xdr:colOff>
+      <xdr:colOff>757080</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>131760</xdr:rowOff>
+      <xdr:rowOff>131040</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3043,8 +3035,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9521280" y="380880"/>
-        <a:ext cx="4906800" cy="3047760"/>
+        <a:off x="9531000" y="380880"/>
+        <a:ext cx="4913280" cy="3047040"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3063,9 +3055,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>757800</xdr:colOff>
+      <xdr:colOff>757080</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>6840</xdr:rowOff>
+      <xdr:rowOff>6120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3073,8 +3065,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9521280" y="3619440"/>
-        <a:ext cx="4906800" cy="3999960"/>
+        <a:off x="9531000" y="3619080"/>
+        <a:ext cx="4913280" cy="3999240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3105,119 +3097,13 @@
 </table>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="129.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="178.59"/>
@@ -3463,8 +3349,8 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3473,12 +3359,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.33"/>
@@ -3495,7 +3381,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>226</v>
@@ -3504,22 +3390,22 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>225</v>
@@ -3533,34 +3419,34 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>310</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>237</v>
@@ -3571,34 +3457,34 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>310</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>104</v>
@@ -3609,34 +3495,34 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>237</v>
@@ -3647,34 +3533,34 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>253</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>237</v>
@@ -3685,34 +3571,34 @@
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>104</v>
@@ -3723,34 +3609,34 @@
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>104</v>
@@ -3761,22 +3647,22 @@
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>230</v>
@@ -3785,10 +3671,10 @@
         <v>253</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>237</v>
@@ -3799,34 +3685,34 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>166</v>
@@ -3837,8 +3723,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3847,12 +3733,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.09"/>
@@ -4257,14 +4143,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F11" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F11" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4273,12 +4159,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N41"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.64"/>
@@ -5974,26 +5860,26 @@
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>K2="Bloqueado"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>K2="No iniciado"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>K2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K41" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K41" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M41" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M41" type="list">
       <formula1>Listas!$B$2:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6002,18 +5888,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M87"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="72.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="72.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="36.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="101.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.33"/>
@@ -6815,6 +6701,63 @@
         <v>357</v>
       </c>
     </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="14"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="14"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="14"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="14"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="14"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="14"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="14"/>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="14"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="14"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="14"/>
+    </row>
+    <row r="74" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B74" s="14"/>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="14"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="14"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="14"/>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="260.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C87" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="J2:J21">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6823,37 +6766,37 @@
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>J2="En progreso"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>J2="Bloqueado"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>J2="No iniciado"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>J2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H20" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H20" type="list">
       <formula1>Listas!$C$2:$C$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I20" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I20" type="list">
       <formula1>Listas!$D$2:$D$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K20" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K20" type="list">
       <formula1>Listas!$B$2:$B$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6863,12 +6806,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="56.13"/>
@@ -6885,67 +6828,67 @@
         <v>220</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>366</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>366</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6955,7 +6898,7 @@
         <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
@@ -6963,7 +6906,7 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -6977,7 +6920,7 @@
         <v>272</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
@@ -6985,7 +6928,7 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -6999,7 +6942,7 @@
         <v>280</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
@@ -7007,7 +6950,7 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -7018,10 +6961,10 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
@@ -7029,7 +6972,7 @@
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -7040,10 +6983,10 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>3</v>
@@ -7051,7 +6994,7 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -7062,10 +7005,10 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4</v>
@@ -7073,7 +7016,7 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="3" t="s">
@@ -7084,10 +7027,10 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>4</v>
@@ -7095,7 +7038,7 @@
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="s">
@@ -7106,10 +7049,10 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
@@ -7117,7 +7060,7 @@
       <c r="D11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="s">
@@ -7128,10 +7071,10 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>3</v>
@@ -7139,7 +7082,7 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
@@ -7153,7 +7096,7 @@
         <v>334</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
@@ -7161,7 +7104,7 @@
       <c r="D13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="s">
@@ -7172,10 +7115,10 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
@@ -7183,7 +7126,7 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="3" t="s">
@@ -7194,10 +7137,10 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
@@ -7216,10 +7159,10 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -7231,17 +7174,17 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -7253,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -7263,7 +7206,7 @@
         <v>348</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>2</v>
@@ -7288,10 +7231,10 @@
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>F2="En progreso"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>F2="Bloqueado"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>F2="No iniciado"</formula>
     </cfRule>
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7307,20 +7250,20 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{904C8EBB-B655-4444-83BD-584A58B0C0B5}</x14:id>
+          <x14:id>{D6DEC475-22AB-4C2F-B295-48816196CBC8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F14" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F14" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7329,7 +7272,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{904C8EBB-B655-4444-83BD-584A58B0C0B5}">
+          <x14:cfRule type="dataBar" id="{D6DEC475-22AB-4C2F-B295-48816196CBC8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7346,12 +7289,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.17"/>
@@ -7365,28 +7308,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -7413,10 +7356,10 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7433,7 +7376,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Matriz_RV32I!B2:B100)</f>
@@ -7454,7 +7397,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7475,9 +7418,9 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="B6" s="15" t="n">
+        <v>399</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
         <v>0</v>
       </c>
@@ -7496,11 +7439,11 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B7" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(Cobertura_Modulos!F2:F100,"Completado")/COUNTIF(Cobertura_Modulos!F2:F100,"&lt;&gt;N/A"),0)</f>
-        <v>0</v>
+        <v>0.0206185567010309</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -7517,7 +7460,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF(Hazards_Forwarding!L2:L100,"Completado")</f>
@@ -7538,10 +7481,10 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">COUNTIF(Escenarios_Prueba!J2:J106,"Completado")</f>
+        <f aca="false">COUNTIF(Escenarios_Prueba!J2:J120,"Completado")</f>
         <v>0</v>
       </c>
       <c r="C9" s="3"/>
@@ -7562,17 +7505,17 @@
         <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -7595,13 +7538,13 @@
       <c r="D11" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D11,Cobertura_Modulos!A:A,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D11,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D11,Cobertura_Modulos!A:A,0)),0)</f>
-        <v>0/4</v>
+        <v>4/4</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -7614,7 +7557,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"En progreso")</f>
@@ -7624,13 +7567,13 @@
       <c r="D12" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D12,Cobertura_Modulos!A:A,0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="3" t="str">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!D:D,MATCH(D12,Cobertura_Modulos!A:A,0)),0)&amp;"/"&amp;IFERROR(INDEX(Cobertura_Modulos!C:C,MATCH(D12,Cobertura_Modulos!A:A,0)),0)</f>
-        <v>0/2</v>
+        <v>2/2</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -7643,7 +7586,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Bloqueado")</f>
@@ -7653,7 +7596,7 @@
       <c r="D13" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D13,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7672,7 +7615,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7682,7 +7625,7 @@
       <c r="D14" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D14,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7701,7 +7644,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"N/A")</f>
@@ -7711,7 +7654,7 @@
       <c r="D15" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D15,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7730,16 +7673,16 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E16" s="15" t="n">
+        <v>371</v>
+      </c>
+      <c r="E16" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7758,7 +7701,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Documentos_Entradas!D2:D100,"Sí")</f>
@@ -7766,9 +7709,9 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E17" s="15" t="n">
+        <v>373</v>
+      </c>
+      <c r="E17" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7787,7 +7730,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">COUNTIFS(Documentos_Entradas!D2:D100,"Sí",Documentos_Entradas!I2:I100,"Completo")</f>
@@ -7795,9 +7738,9 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E18" s="15" t="n">
+        <v>375</v>
+      </c>
+      <c r="E18" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7816,7 +7759,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTA(MMIO_Interrupts_Traps!A2:A100)</f>
@@ -7824,9 +7767,9 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="E19" s="15" t="n">
+        <v>377</v>
+      </c>
+      <c r="E19" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7845,7 +7788,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(MMIO_Interrupts_Traps!J2:J100,"Completado")</f>
@@ -7853,9 +7796,9 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E20" s="15" t="n">
+        <v>381</v>
+      </c>
+      <c r="E20" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7874,9 +7817,9 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="B21" s="15" t="n">
+        <v>412</v>
+      </c>
+      <c r="B21" s="16" t="n">
         <f aca="false">IFERROR(B20/B19,0)</f>
         <v>0</v>
       </c>
@@ -7884,7 +7827,7 @@
       <c r="D21" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D21,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7906,9 +7849,9 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E22" s="15" t="n">
+        <v>386</v>
+      </c>
+      <c r="E22" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7927,12 +7870,12 @@
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
-      <c r="B23" s="15"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D23,Cobertura_Modulos!A:A,0)),0)</f>
         <v>0</v>
       </c>
@@ -7962,14 +7905,14 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{6DC2ACFC-46D7-4A79-8892-582C30E3B6B1}</x14:id>
+          <x14:id>{9389F077-D978-4CA6-81D8-80E9BB5053D1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7979,7 +7922,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{6DC2ACFC-46D7-4A79-8892-582C30E3B6B1}">
+          <x14:cfRule type="dataBar" id="{9389F077-D978-4CA6-81D8-80E9BB5053D1}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7996,12 +7939,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.12"/>
@@ -8018,31 +7961,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>92</v>
@@ -8053,22 +7996,22 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
@@ -8076,7 +8019,7 @@
       <c r="H2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="15" t="n">
+      <c r="I2" s="16" t="n">
         <f aca="false">IF(G2=0,0,H2/G2)</f>
         <v>0</v>
       </c>
@@ -8087,22 +8030,22 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>8</v>
@@ -8110,7 +8053,7 @@
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="15" t="n">
+      <c r="I3" s="16" t="n">
         <f aca="false">IF(G3=0,0,H3/G3)</f>
         <v>0</v>
       </c>
@@ -8121,22 +8064,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>4</v>
@@ -8144,7 +8087,7 @@
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="15" t="n">
+      <c r="I4" s="16" t="n">
         <f aca="false">IF(G4=0,0,H4/G4)</f>
         <v>0</v>
       </c>
@@ -8155,22 +8098,22 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8</v>
@@ -8178,7 +8121,7 @@
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="16" t="n">
         <f aca="false">IF(G5=0,0,H5/G5)</f>
         <v>0</v>
       </c>
@@ -8189,22 +8132,22 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>6</v>
@@ -8212,7 +8155,7 @@
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="15" t="n">
+      <c r="I6" s="16" t="n">
         <f aca="false">IF(G6=0,0,H6/G6)</f>
         <v>0</v>
       </c>
@@ -8223,22 +8166,22 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -8246,7 +8189,7 @@
       <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="16" t="n">
         <f aca="false">IF(G7=0,0,H7/G7)</f>
         <v>0</v>
       </c>
@@ -8257,16 +8200,16 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>67</v>
@@ -8280,7 +8223,7 @@
       <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="15" t="n">
+      <c r="I8" s="16" t="n">
         <f aca="false">IF(G8=0,0,H8/G8)</f>
         <v>0</v>
       </c>
@@ -8291,16 +8234,16 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -8314,7 +8257,7 @@
       <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="16" t="n">
         <f aca="false">IF(G9=0,0,H9/G9)</f>
         <v>0</v>
       </c>
@@ -8325,16 +8268,16 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>67</v>
@@ -8348,7 +8291,7 @@
       <c r="H10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="16" t="n">
         <f aca="false">IF(G10=0,0,H10/G10)</f>
         <v>0</v>
       </c>
@@ -8359,16 +8302,16 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>67</v>
@@ -8382,7 +8325,7 @@
       <c r="H11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="16" t="n">
         <f aca="false">IF(G11=0,0,H11/G11)</f>
         <v>0</v>
       </c>
@@ -8418,20 +8361,20 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{BDFDABC0-B840-44F9-8AED-17A2D0AAC8E3}</x14:id>
+          <x14:id>{77D06EF9-6D13-4C6A-A66A-273C8870D886}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J11" type="list">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J11" type="list">
       <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8443,7 +8386,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BDFDABC0-B840-44F9-8AED-17A2D0AAC8E3}">
+          <x14:cfRule type="dataBar" id="{77D06EF9-6D13-4C6A-A66A-273C8870D886}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8460,12 +8403,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="22.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="5" style="1" width="10.77"/>
@@ -8479,10 +8422,10 @@
         <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8501,13 +8444,13 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>38</v>
@@ -8515,7 +8458,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>212</v>
@@ -8524,12 +8467,12 @@
         <v>349</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>237</v>
@@ -8541,7 +8484,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -8553,7 +8496,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -8567,8 +8510,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8577,12 +8520,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.86"/>
@@ -8590,36 +8533,36 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="108.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="110.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="110.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="69.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="69.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="13" style="1" width="10.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>348</v>
@@ -8628,7 +8571,7 @@
         <v>92</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>33</v>
@@ -8637,62 +8580,62 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>102</v>
@@ -8703,28 +8646,28 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>102</v>
@@ -8735,25 +8678,25 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>140</v>
@@ -8767,28 +8710,28 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>102</v>
@@ -8802,25 +8745,25 @@
         <v>253</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>102</v>
@@ -8831,28 +8774,28 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>102</v>
@@ -8863,28 +8806,28 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>504</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>102</v>
@@ -8898,25 +8841,25 @@
         <v>334</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>102</v>
@@ -8930,25 +8873,25 @@
         <v>341</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>102</v>
@@ -8959,42 +8902,42 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L12" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio_Guia" sheetId="1" state="visible" r:id="rId2"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="607">
   <si>
     <t xml:space="preserve">Plantilla de verificación RV32I para core pipeline de 5 etapas con IF de 2 ciclos (BRAM síncrona)</t>
   </si>
@@ -1161,6 +1161,69 @@
   </si>
   <si>
     <t xml:space="preserve">WB → OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+	addi x1, x0, 7
+	add  x2, x1, x1
+	sub  x3, x2, x1      
+	ori  x4, x3, 3
+	andi x5, x4, 15
+	//jal  x0, done
+	.word 0xFFFFFFFF   # illegal
+Done:
+	jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">illegal OP = 1 → OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    # 1) x0 debe ignorar escritura
+    addi x0, x0, 123
+    # 2) verificar lectura de x0
+    addi x1, x0, 0          # x1 = 0
+    addi x2, x0, 5          # x2 = 5
+    # 3) escritura normal
+    addi x3, x0, 10         # x3 = 10
+    addi x4, x0, 20         # x4 = 20
+    # 4) lectura de dos operandos desde regfile
+    add  x5, x3, x4         # x5 = 30
+    # 5) verificar que registros previos conservan valor
+    addi x6, x3, 0          # x6 = 10
+    addi x7, x4, 0          # x7 = 20
+    # 6) probar reescritura de un registro
+    addi x3, x0, 99         # x3 = 99
+    add  x8, x3, x1         # x8 = 99 + 0 = 99
+    # 7) comprobar que x0 sigue siendo 0 incluso después
+    addi x9, x0, 0          # x9 = 0
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+.section .text.start
+.globl _start
+_start:
+    addi x1, x0, -1          # I-type
+    lui  x2, 0x12345         # U-type
+    auipc x3, 0              # U-type relativo a PC
+    beq  x0, x0, label_b     # B-type
+    addi x4, x0, 99          # wrong-path
+label_b:
+    jal  x5, label_j         # J-type
+    addi x6, x0, 88          # wrong-path
+label_j:
+    addi x7, x0, 7
+done:
+    jal x0, done</t>
   </si>
   <si>
     <t xml:space="preserve">Descripción</t>
@@ -2115,7 +2178,7 @@
     <cellStyle name="Percent" xfId="19" builtinId="5" customBuiltin="false"/>
     <cellStyle name="Excel Built-in Explanatory Text" xfId="20" builtinId="53" customBuiltin="true"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -2142,13 +2205,6 @@
         <bottom/>
         <diagonal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Lohit Devanagari"/>
-        <charset val="1"/>
-        <family val="2"/>
-      </font>
     </dxf>
   </dxfs>
   <colors>
@@ -2344,11 +2400,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="8450327"/>
-        <c:axId val="57998876"/>
+        <c:axId val="26079165"/>
+        <c:axId val="2698842"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8450327"/>
+        <c:axId val="26079165"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2391,14 +2447,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57998876"/>
+        <c:crossAx val="2698842"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57998876"/>
+        <c:axId val="2698842"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2441,7 +2497,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8450327"/>
+        <c:crossAx val="26079165"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2673,11 +2729,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="84834643"/>
-        <c:axId val="60193167"/>
+        <c:axId val="82614165"/>
+        <c:axId val="32785498"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="84834643"/>
+        <c:axId val="82614165"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2720,14 +2776,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60193167"/>
+        <c:crossAx val="32785498"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60193167"/>
+        <c:axId val="32785498"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2770,7 +2826,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84834643"/>
+        <c:crossAx val="82614165"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2835,9 +2891,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6753600</xdr:colOff>
+      <xdr:colOff>6753240</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>71280</xdr:rowOff>
+      <xdr:rowOff>70920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2851,7 +2907,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1969560" y="9150480"/>
-          <a:ext cx="18123840" cy="3265560"/>
+          <a:ext cx="18123480" cy="3265200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2872,9 +2928,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>7016760</xdr:colOff>
+      <xdr:colOff>7016400</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>155520</xdr:rowOff>
+      <xdr:rowOff>155160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2888,7 +2944,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2058120" y="5149800"/>
-          <a:ext cx="18298440" cy="3366000"/>
+          <a:ext cx="18298080" cy="3365640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2909,9 +2965,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6950160</xdr:colOff>
+      <xdr:colOff>6949800</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>176040</xdr:rowOff>
+      <xdr:rowOff>175680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2925,7 +2981,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2020680" y="13147920"/>
-          <a:ext cx="18269280" cy="3002760"/>
+          <a:ext cx="18268920" cy="3002400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2946,9 +3002,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6945480</xdr:colOff>
+      <xdr:colOff>6945120</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>29520</xdr:rowOff>
+      <xdr:rowOff>29160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2962,7 +3018,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1981440" y="16470360"/>
-          <a:ext cx="18303840" cy="3686040"/>
+          <a:ext cx="18303480" cy="3685680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2983,9 +3039,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>6892200</xdr:colOff>
+      <xdr:colOff>6891840</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>58320</xdr:rowOff>
+      <xdr:rowOff>86040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2999,7 +3055,81 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2006280" y="20805120"/>
-          <a:ext cx="18225720" cy="4129920"/>
+          <a:ext cx="18225360" cy="4129560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>59040</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>156600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 6" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3263760" y="25773120"/>
+          <a:ext cx="18264960" cy="4131720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1076040</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>74160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1144800</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>24840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagen 7" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4339800" y="30394080"/>
+          <a:ext cx="18274680" cy="4408200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3025,18 +3155,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>757080</xdr:colOff>
+      <xdr:colOff>756720</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>131040</xdr:rowOff>
+      <xdr:rowOff>130680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart"/>
+        <xdr:cNvPr id="7" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9531000" y="380880"/>
-        <a:ext cx="4913280" cy="3047040"/>
+        <a:ext cx="4912920" cy="3046680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3055,18 +3185,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>757080</xdr:colOff>
+      <xdr:colOff>756720</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>6120</xdr:rowOff>
+      <xdr:rowOff>5760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart"/>
+        <xdr:cNvPr id="8" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9531000" y="3619080"/>
-        <a:ext cx="4913280" cy="3999240"/>
+        <a:ext cx="4912920" cy="3998880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3381,7 +3511,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>226</v>
@@ -3390,22 +3520,22 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>225</v>
@@ -3419,34 +3549,34 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>310</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>237</v>
@@ -3457,34 +3587,34 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>310</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>104</v>
@@ -3495,34 +3625,34 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>237</v>
@@ -3533,34 +3663,34 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>253</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>237</v>
@@ -3571,34 +3701,34 @@
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>104</v>
@@ -3609,34 +3739,34 @@
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>575</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>104</v>
@@ -3647,22 +3777,22 @@
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>230</v>
@@ -3671,10 +3801,10 @@
         <v>253</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>237</v>
@@ -3685,34 +3815,34 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>166</v>
@@ -5892,7 +6022,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
@@ -6753,9 +6883,47 @@
         <v>358</v>
       </c>
     </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="13" t="s">
+        <v>359</v>
+      </c>
+    </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C87" s="13" t="s">
-        <v>359</v>
+      <c r="C87" s="0"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="148" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="351" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="14" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="227" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="14" t="s">
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -6777,16 +6945,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
+    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
+      <formula1>Listas!$A$2:$A$6</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H20" type="list">
       <formula1>Listas!$C$2:$C$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I20" type="list">
       <formula1>Listas!$D$2:$D$4</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J20" type="list">
-      <formula1>Listas!$A$2:$A$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K20" type="list">
@@ -6828,22 +6996,22 @@
         <v>220</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>33</v>
@@ -6854,7 +7022,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -6866,7 +7034,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -6876,7 +7044,7 @@
         <v>253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
@@ -6888,7 +7056,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6898,7 +7066,7 @@
         <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
@@ -6920,7 +7088,7 @@
         <v>272</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
@@ -6942,7 +7110,7 @@
         <v>280</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
@@ -6961,10 +7129,10 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
@@ -6983,10 +7151,10 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>3</v>
@@ -7005,10 +7173,10 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4</v>
@@ -7027,10 +7195,10 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>4</v>
@@ -7049,10 +7217,10 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
@@ -7071,10 +7239,10 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>3</v>
@@ -7096,7 +7264,7 @@
         <v>334</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
@@ -7115,10 +7283,10 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
@@ -7137,10 +7305,10 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
@@ -7159,10 +7327,10 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -7174,17 +7342,17 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -7196,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -7206,7 +7374,7 @@
         <v>348</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>2</v>
@@ -7250,7 +7418,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D6DEC475-22AB-4C2F-B295-48816196CBC8}</x14:id>
+          <x14:id>{A59778A0-CD65-41F4-B5F2-ED996FDD3447}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7272,7 +7440,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D6DEC475-22AB-4C2F-B295-48816196CBC8}">
+          <x14:cfRule type="dataBar" id="{A59778A0-CD65-41F4-B5F2-ED996FDD3447}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7308,28 +7476,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -7356,10 +7524,10 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7376,7 +7544,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Matriz_RV32I!B2:B100)</f>
@@ -7397,7 +7565,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7418,7 +7586,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
@@ -7439,7 +7607,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(Cobertura_Modulos!F2:F100,"Completado")/COUNTIF(Cobertura_Modulos!F2:F100,"&lt;&gt;N/A"),0)</f>
@@ -7460,7 +7628,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF(Hazards_Forwarding!L2:L100,"Completado")</f>
@@ -7481,7 +7649,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">COUNTIF(Escenarios_Prueba!J2:J120,"Completado")</f>
@@ -7505,17 +7673,17 @@
         <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -7557,7 +7725,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"En progreso")</f>
@@ -7586,7 +7754,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Bloqueado")</f>
@@ -7615,7 +7783,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7644,7 +7812,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"N/A")</f>
@@ -7673,14 +7841,14 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7701,7 +7869,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Documentos_Entradas!D2:D100,"Sí")</f>
@@ -7709,7 +7877,7 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7730,7 +7898,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">COUNTIFS(Documentos_Entradas!D2:D100,"Sí",Documentos_Entradas!I2:I100,"Completo")</f>
@@ -7738,7 +7906,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7759,7 +7927,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTA(MMIO_Interrupts_Traps!A2:A100)</f>
@@ -7767,7 +7935,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7788,7 +7956,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(MMIO_Interrupts_Traps!J2:J100,"Completado")</f>
@@ -7796,7 +7964,7 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7817,7 +7985,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">IFERROR(B20/B19,0)</f>
@@ -7849,7 +8017,7 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7905,7 +8073,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9389F077-D978-4CA6-81D8-80E9BB5053D1}</x14:id>
+          <x14:id>{5F203F51-B6F5-40F8-8AAE-FF76FE5D909B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7922,7 +8090,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9389F077-D978-4CA6-81D8-80E9BB5053D1}">
+          <x14:cfRule type="dataBar" id="{5F203F51-B6F5-40F8-8AAE-FF76FE5D909B}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7961,31 +8129,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>92</v>
@@ -7996,22 +8164,22 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
@@ -8030,22 +8198,22 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>8</v>
@@ -8064,22 +8232,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>4</v>
@@ -8098,22 +8266,22 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8</v>
@@ -8132,22 +8300,22 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>6</v>
@@ -8166,22 +8334,22 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -8200,16 +8368,16 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>67</v>
@@ -8234,16 +8402,16 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -8268,16 +8436,16 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>67</v>
@@ -8302,16 +8470,16 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>67</v>
@@ -8361,7 +8529,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{77D06EF9-6D13-4C6A-A66A-273C8870D886}</x14:id>
+          <x14:id>{923F2876-1269-4ECA-8A7C-1B7BE2C72EC0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8386,7 +8554,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{77D06EF9-6D13-4C6A-A66A-273C8870D886}">
+          <x14:cfRule type="dataBar" id="{923F2876-1269-4ECA-8A7C-1B7BE2C72EC0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8422,10 +8590,10 @@
         <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8444,13 +8612,13 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>38</v>
@@ -8458,7 +8626,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>212</v>
@@ -8467,12 +8635,12 @@
         <v>349</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>237</v>
@@ -8484,7 +8652,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -8496,7 +8664,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -8544,25 +8712,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>348</v>
@@ -8571,7 +8739,7 @@
         <v>92</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>33</v>
@@ -8580,62 +8748,62 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>102</v>
@@ -8646,28 +8814,28 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>102</v>
@@ -8678,25 +8846,25 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>140</v>
@@ -8710,28 +8878,28 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>102</v>
@@ -8745,25 +8913,25 @@
         <v>253</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>102</v>
@@ -8774,28 +8942,28 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>102</v>
@@ -8806,28 +8974,28 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>102</v>
@@ -8841,25 +9009,25 @@
         <v>334</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>102</v>
@@ -8873,25 +9041,25 @@
         <v>341</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>102</v>
@@ -8902,35 +9070,35 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="L12" s="3"/>
     </row>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="618">
   <si>
     <t xml:space="preserve">Plantilla de verificación RV32I para core pipeline de 5 etapas con IF de 2 ciclos (BRAM síncrona)</t>
   </si>
@@ -740,6 +740,9 @@
   </si>
   <si>
     <t xml:space="preserve">Dirigido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completado</t>
   </si>
   <si>
     <t xml:space="preserve">Crítica</t>
@@ -1226,6 +1229,192 @@
     jal x0, done</t>
   </si>
   <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    addi x1, x0, 1
+    slli x2, x1, 3
+    srli x3, x2, 1
+    srai x4, x3, 1
+    addi x5, x0, -1
+    srai x6, x5, 4
+    srli x7, x5, 4
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    addi x1, x0, 5
+    addi x2, x0, 5
+    beq  x1, x2, beq_ok
+    addi x3, x0, 11          # wrong-path
+beq_ok:
+    addi x4, x0, 1
+    bne  x1, x2, bne_fail
+    addi x5, x0, 2           # sí debe ejecutar
+    jal  x0, done
+bne_fail:
+    addi x6, x0, 99
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    jal  x1, target
+    addi x2, x0, 22          # wrong-path
+target:
+    addi x3, x1, 0
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    auipc x10, 0
+    addi  x10, x10, target - _start
+    jalr  x1, x10, 0
+    addi  x2, x0, 22         # wrong-path
+target:
+    addi  x3, x0, 77
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    addi x1, x0, 9
+    add  x2, x1, x1
+    addi x3, x2, 1
+    add  x4, x3, x2
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    addi x1, x0, 42
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    sw   x1, 0(x10)
+    lw   x2, 0(x10)
+    addi x3, x2, 1
+    add  x4, x3, x2
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    addi x1, x0, -1
+    sb   x1, 0(x10)
+    lb   x2, 0(x10)
+    lbu  x3, 0(x10)
+    lui  x4, 0x00008
+    sh   x4, 4(x10)
+    lh   x5, 4(x10)
+    lhu  x6, 4(x10)
+    sw   x4, 8(x10)
+    lw   x7, 8(x10)
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    addi x1, x0, 0x11
+    sb   x1, 0(x10)
+    lui  x2, 0x00002         # 0x00002000
+    addi x2, x2, 0x22
+    sh   x2, 4(x10)
+    lui  x3, 0x12345
+    addi x3, x3, 0x678
+    sw   x3, 8(x10)
+    lb   x4, 0(x10)
+    lh   x5, 4(x10)
+    lw   x6, 8(x10)
+done:
+    jal x0, done
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    addi x1, x0, 7           # fuente ALU
+    lui  x2, 0x12345         # fuente IMM/U
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    sw   x1, 0(x10)
+    lw   x3, 0(x10)          # fuente MEM
+    jal  x4, target          # fuente PC+4
+    addi x5, x0, 99          # wrong-path
+target:
+    addi x6, x0, 1
+done:
+    jal x0, done
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    addi x1, x0, 0
+    sw   x1, 0(x10)
+    lw   x2, 0(x10)
+    beq  x2, x0, target
+    addi x3, x2, 1           # depende de lw y además está en wrong-path
+target:
+    addi x4, x0, 4
+done:
+    jal x0, done
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+.equ RAM_BASE, 0x00000100
+_start:
+    addi x1, x0, 5
+    addi x2, x0, 6
+    add  x3, x1, x2          # 11
+    addi x4, x3, 1           # 12
+    lui  x10, %hi(RAM_BASE)
+    addi x10, x10, %lo(RAM_BASE)
+    sw   x4, 0(x10)
+    lw   x5, 0(x10)          # 12
+    addi x6, x5, 1           # 13
+    beq  x6, x4, skip
+    addi x7, x0, 77          # sí ejecuta si beq no tomado
+skip:
+    jal  x8, target
+    addi x9, x0, 99          # wrong-path
+target:
+    addi x11, x0, 11
+done:
+    jal x0, done</t>
+  </si>
+  <si>
     <t xml:space="preserve">Descripción</t>
   </si>
   <si>
@@ -1242,9 +1431,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fetch, PC, reset vector, redirect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completado</t>
   </si>
   <si>
     <t xml:space="preserve">Registro de pipeline y flush/hold</t>
@@ -2270,7 +2456,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2400,11 +2586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="26079165"/>
-        <c:axId val="2698842"/>
+        <c:axId val="85059597"/>
+        <c:axId val="23076913"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26079165"/>
+        <c:axId val="85059597"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2447,14 +2633,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2698842"/>
+        <c:crossAx val="23076913"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2698842"/>
+        <c:axId val="23076913"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2497,7 +2683,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26079165"/>
+        <c:crossAx val="85059597"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2551,7 +2737,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2729,11 +2915,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="82614165"/>
-        <c:axId val="32785498"/>
+        <c:axId val="42077028"/>
+        <c:axId val="93950861"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82614165"/>
+        <c:axId val="42077028"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2776,14 +2962,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32785498"/>
+        <c:crossAx val="93950861"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32785498"/>
+        <c:axId val="93950861"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2826,7 +3012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82614165"/>
+        <c:crossAx val="42077028"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2884,16 +3070,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1309320</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>10440</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1366200</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>173160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>6753240</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1443960</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>70920</xdr:rowOff>
+      <xdr:rowOff>54000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2906,8 +3092,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1969560" y="9150480"/>
-          <a:ext cx="18123480" cy="3265200"/>
+          <a:off x="4629960" y="9009720"/>
+          <a:ext cx="18283680" cy="3294000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2921,16 +3107,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>51840</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1378800</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>222480</xdr:rowOff>
+      <xdr:rowOff>125280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>7016400</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1470960</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>155160</xdr:rowOff>
+      <xdr:rowOff>58320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2943,7 +3129,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2058120" y="5149800"/>
+          <a:off x="4642560" y="4957560"/>
           <a:ext cx="18298080" cy="3365640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2958,16 +3144,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>14400</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>41040</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1406880</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>147600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>6949800</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1469880</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>175680</xdr:rowOff>
+      <xdr:rowOff>91800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2980,7 +3166,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2020680" y="13147920"/>
+          <a:off x="4670640" y="12968640"/>
           <a:ext cx="18268920" cy="3002400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2995,16 +3181,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1321200</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1394280</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>114840</xdr:rowOff>
+      <xdr:rowOff>172080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>6945120</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>14760</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>29160</xdr:rowOff>
+      <xdr:rowOff>86400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3017,7 +3203,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1981440" y="16470360"/>
+          <a:off x="4658040" y="16432200"/>
           <a:ext cx="18303480" cy="3685680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3032,16 +3218,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1431720</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>117360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>6891840</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1451160</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>40680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3054,7 +3240,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2006280" y="20805120"/>
+          <a:off x="4695480" y="20664360"/>
           <a:ext cx="18225360" cy="4129560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3070,15 +3256,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1403640</xdr:colOff>
       <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>107640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>59040</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>156600</xdr:rowOff>
+      <xdr:colOff>1462680</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>73800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3091,7 +3277,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3263760" y="25773120"/>
+          <a:off x="4667400" y="25785720"/>
           <a:ext cx="18264960" cy="4131720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3107,15 +3293,15 @@
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1076040</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>74160</xdr:rowOff>
+      <xdr:colOff>1404360</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>116280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1144800</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>24840</xdr:rowOff>
+      <xdr:colOff>1473120</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>4334040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3128,8 +3314,119 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4339800" y="30394080"/>
+          <a:off x="4668120" y="30150360"/>
           <a:ext cx="18274680" cy="4408200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1403640</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>177480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1452960</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>12600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 8" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4667400" y="35050320"/>
+          <a:ext cx="18255240" cy="6337440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1404000</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>18000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1463040</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>150840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 9" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4667760" y="42155280"/>
+          <a:ext cx="18264960" cy="4971240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1364400</xdr:colOff>
+      <xdr:row>148</xdr:row>
+      <xdr:rowOff>50760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1423440</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>30600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 10" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4628160" y="47598120"/>
+          <a:ext cx="18264960" cy="4958280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3161,7 +3458,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Chart"/>
+        <xdr:cNvPr id="10" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3191,7 +3488,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart"/>
+        <xdr:cNvPr id="11" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3511,7 +3808,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>226</v>
@@ -3520,22 +3817,22 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>225</v>
@@ -3549,37 +3846,37 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>102</v>
@@ -3587,34 +3884,34 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>104</v>
@@ -3625,37 +3922,37 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>102</v>
@@ -3663,37 +3960,37 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>102</v>
@@ -3701,34 +3998,34 @@
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>104</v>
@@ -3739,34 +4036,34 @@
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>104</v>
@@ -3777,37 +4074,37 @@
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>230</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>102</v>
@@ -3815,34 +4112,34 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>166</v>
@@ -6022,7 +6319,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M108"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
@@ -6078,7 +6375,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
         <v>229</v>
       </c>
@@ -6107,39 +6404,39 @@
         <v>37</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>236</v>
@@ -6148,35 +6445,35 @@
         <v>37</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L3" s="12"/>
       <c r="M3" s="13"/>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>230</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>236</v>
@@ -6185,35 +6482,35 @@
         <v>37</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L4" s="12"/>
       <c r="M4" s="13"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>236</v>
@@ -6222,7 +6519,7 @@
         <v>37</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>104</v>
@@ -6230,27 +6527,27 @@
       <c r="L5" s="12"/>
       <c r="M5" s="13"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>236</v>
@@ -6259,35 +6556,35 @@
         <v>37</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>102</v>
+        <v>237</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>236</v>
@@ -6306,28 +6603,28 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>37</v>
@@ -6336,32 +6633,32 @@
         <v>102</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L8" s="12"/>
       <c r="M8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>236</v>
@@ -6380,25 +6677,25 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>236</v>
@@ -6417,7 +6714,7 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>122</v>
@@ -6426,16 +6723,16 @@
         <v>54</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>236</v>
@@ -6454,25 +6751,25 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>236</v>
@@ -6491,25 +6788,25 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>236</v>
@@ -6528,25 +6825,25 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>236</v>
@@ -6558,32 +6855,32 @@
         <v>102</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>236</v>
@@ -6595,32 +6892,32 @@
         <v>102</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="13"/>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>236</v>
@@ -6639,25 +6936,25 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>140</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>236</v>
@@ -6676,25 +6973,25 @@
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>236</v>
@@ -6713,25 +7010,25 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>236</v>
@@ -6750,28 +7047,28 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>349</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>37</v>
@@ -6780,7 +7077,7 @@
         <v>102</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="13"/>
@@ -6792,7 +7089,7 @@
     </row>
     <row r="26" customFormat="false" ht="102.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6800,12 +7097,12 @@
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="147.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6813,22 +7110,22 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6875,17 +7172,17 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="260.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6893,37 +7190,147 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="148" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="351" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="227" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="171" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="227" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="14" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="137" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="14" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="160" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B168" s="14" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="126" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B173" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="193" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B178" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="272" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B182" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="306" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B187" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="261" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B192" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="250" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="14" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -6996,22 +7403,22 @@
         <v>220</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>33</v>
@@ -7022,7 +7429,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -7034,17 +7441,17 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
@@ -7056,17 +7463,17 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
@@ -7085,10 +7492,10 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
@@ -7107,10 +7514,10 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
@@ -7129,10 +7536,10 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
@@ -7151,10 +7558,10 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>3</v>
@@ -7173,10 +7580,10 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4</v>
@@ -7195,10 +7602,10 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>4</v>
@@ -7217,10 +7624,10 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
@@ -7239,10 +7646,10 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>3</v>
@@ -7261,10 +7668,10 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
@@ -7283,10 +7690,10 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
@@ -7305,10 +7712,10 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
@@ -7327,10 +7734,10 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -7342,17 +7749,17 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -7364,17 +7771,17 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>2</v>
@@ -7418,7 +7825,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A59778A0-CD65-41F4-B5F2-ED996FDD3447}</x14:id>
+          <x14:id>{55815B50-D412-4755-88D3-8EB016D0A0D4}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7440,7 +7847,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A59778A0-CD65-41F4-B5F2-ED996FDD3447}">
+          <x14:cfRule type="dataBar" id="{55815B50-D412-4755-88D3-8EB016D0A0D4}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -7476,28 +7883,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -7524,10 +7931,10 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7544,7 +7951,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Matriz_RV32I!B2:B100)</f>
@@ -7565,7 +7972,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7586,7 +7993,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
@@ -7607,7 +8014,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(Cobertura_Modulos!F2:F100,"Completado")/COUNTIF(Cobertura_Modulos!F2:F100,"&lt;&gt;N/A"),0)</f>
@@ -7628,7 +8035,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF(Hazards_Forwarding!L2:L100,"Completado")</f>
@@ -7649,11 +8056,11 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">COUNTIF(Escenarios_Prueba!J2:J120,"Completado")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -7673,17 +8080,17 @@
         <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -7725,7 +8132,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"En progreso")</f>
@@ -7733,7 +8140,7 @@
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D12,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7754,7 +8161,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Bloqueado")</f>
@@ -7762,7 +8169,7 @@
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E13" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D13,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7783,7 +8190,7 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -7791,7 +8198,7 @@
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E14" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D14,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7812,7 +8219,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"N/A")</f>
@@ -7820,7 +8227,7 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D15,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7841,14 +8248,14 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7869,7 +8276,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Documentos_Entradas!D2:D100,"Sí")</f>
@@ -7877,7 +8284,7 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7898,7 +8305,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">COUNTIFS(Documentos_Entradas!D2:D100,"Sí",Documentos_Entradas!I2:I100,"Completo")</f>
@@ -7906,7 +8313,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7927,7 +8334,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTA(MMIO_Interrupts_Traps!A2:A100)</f>
@@ -7935,7 +8342,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7956,7 +8363,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(MMIO_Interrupts_Traps!J2:J100,"Completado")</f>
@@ -7964,7 +8371,7 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
@@ -7985,7 +8392,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">IFERROR(B20/B19,0)</f>
@@ -7993,7 +8400,7 @@
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E21" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D21,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8017,7 +8424,7 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8041,7 +8448,7 @@
       <c r="B23" s="16"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D23,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8073,7 +8480,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5F203F51-B6F5-40F8-8AAE-FF76FE5D909B}</x14:id>
+          <x14:id>{F25A8718-8B2B-462B-B0E9-9CA626634CC6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8090,7 +8497,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5F203F51-B6F5-40F8-8AAE-FF76FE5D909B}">
+          <x14:cfRule type="dataBar" id="{F25A8718-8B2B-462B-B0E9-9CA626634CC6}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8129,31 +8536,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>92</v>
@@ -8164,22 +8571,22 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
@@ -8198,22 +8605,22 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>8</v>
@@ -8232,22 +8639,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>4</v>
@@ -8266,22 +8673,22 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8</v>
@@ -8300,22 +8707,22 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>6</v>
@@ -8334,22 +8741,22 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -8368,16 +8775,16 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>67</v>
@@ -8402,16 +8809,16 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -8436,16 +8843,16 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>67</v>
@@ -8470,16 +8877,16 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>67</v>
@@ -8529,7 +8936,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{923F2876-1269-4ECA-8A7C-1B7BE2C72EC0}</x14:id>
+          <x14:id>{3F4FEAB0-80DC-49F9-92D2-31BEEC461484}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8554,7 +8961,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{923F2876-1269-4ECA-8A7C-1B7BE2C72EC0}">
+          <x14:cfRule type="dataBar" id="{3F4FEAB0-80DC-49F9-92D2-31BEEC461484}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8590,10 +8997,10 @@
         <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8612,13 +9019,13 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>38</v>
@@ -8626,37 +9033,37 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -8664,7 +9071,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -8712,34 +9119,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>92</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>33</v>
@@ -8748,62 +9155,62 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>102</v>
@@ -8814,28 +9221,28 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>102</v>
@@ -8846,25 +9253,25 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>140</v>
@@ -8878,28 +9285,28 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>102</v>
@@ -8910,28 +9317,28 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>102</v>
@@ -8942,28 +9349,28 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>102</v>
@@ -8974,28 +9381,28 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>102</v>
@@ -9006,28 +9413,28 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>509</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>102</v>
@@ -9038,28 +9445,28 @@
     </row>
     <row r="11" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>102</v>
@@ -9070,35 +9477,35 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="L12" s="3"/>
     </row>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -2456,7 +2456,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart41.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2586,11 +2586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="85059597"/>
-        <c:axId val="23076913"/>
+        <c:axId val="34139189"/>
+        <c:axId val="54603511"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85059597"/>
+        <c:axId val="34139189"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2633,14 +2633,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23076913"/>
+        <c:crossAx val="54603511"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="23076913"/>
+        <c:axId val="54603511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,7 +2683,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85059597"/>
+        <c:crossAx val="34139189"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2737,7 +2737,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart42.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2915,11 +2915,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42077028"/>
-        <c:axId val="93950861"/>
+        <c:axId val="50367396"/>
+        <c:axId val="3793270"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42077028"/>
+        <c:axId val="50367396"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,14 +2962,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93950861"/>
+        <c:crossAx val="3793270"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93950861"/>
+        <c:axId val="3793270"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,7 +3012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42077028"/>
+        <c:crossAx val="50367396"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -3438,6 +3438,80 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1337760</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>102240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1387080</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>101160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 11" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4601520" y="53008920"/>
+          <a:ext cx="18255240" cy="3908160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1377360</xdr:colOff>
+      <xdr:row>180</xdr:row>
+      <xdr:rowOff>38520</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1446120</xdr:colOff>
+      <xdr:row>192</xdr:row>
+      <xdr:rowOff>32400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 12" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4641120" y="57560400"/>
+          <a:ext cx="18274680" cy="3870000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3458,7 +3532,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="10" name="Chart"/>
+        <xdr:cNvPr id="12" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3488,7 +3562,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart"/>
+        <xdr:cNvPr id="13" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -6319,7 +6393,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M222"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
@@ -7253,83 +7327,105 @@
         <v>368</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+    <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="160" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="14" t="s">
+    <row r="181" customFormat="false" ht="160" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B181" s="14" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="126" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="14" t="s">
+    <row r="195" customFormat="false" ht="126" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B195" s="14" t="s">
         <v>370</v>
-      </c>
-    </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="178" customFormat="false" ht="193" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="14" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="182" customFormat="false" ht="272" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="14" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="306" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="14" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="261" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="14" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="250" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="14" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="193" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="272" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="306" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="261" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B214" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="250" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B200" s="14" t="s">
+    <row r="222" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="14" t="s">
         <v>376</v>
       </c>
     </row>
@@ -7825,7 +7921,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{55815B50-D412-4755-88D3-8EB016D0A0D4}</x14:id>
+          <x14:id>{7BEF86E0-B0F1-4488-A046-EA5776225150}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7847,7 +7943,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{55815B50-D412-4755-88D3-8EB016D0A0D4}">
+          <x14:cfRule type="dataBar" id="{7BEF86E0-B0F1-4488-A046-EA5776225150}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8480,7 +8576,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{F25A8718-8B2B-462B-B0E9-9CA626634CC6}</x14:id>
+          <x14:id>{AB97E071-6A1C-4AC9-8A93-9377AF9A10B0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8497,7 +8593,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{F25A8718-8B2B-462B-B0E9-9CA626634CC6}">
+          <x14:cfRule type="dataBar" id="{AB97E071-6A1C-4AC9-8A93-9377AF9A10B0}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8936,7 +9032,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3F4FEAB0-80DC-49F9-92D2-31BEEC461484}</x14:id>
+          <x14:id>{FA31307F-9FC6-4540-9BEB-DB8960F87D1C}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8961,7 +9057,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3F4FEAB0-80DC-49F9-92D2-31BEEC461484}">
+          <x14:cfRule type="dataBar" id="{FA31307F-9FC6-4540-9BEB-DB8960F87D1C}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -2456,7 +2456,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2586,11 +2586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34139189"/>
-        <c:axId val="54603511"/>
+        <c:axId val="93862686"/>
+        <c:axId val="89121999"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34139189"/>
+        <c:axId val="93862686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2633,14 +2633,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54603511"/>
+        <c:crossAx val="89121999"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54603511"/>
+        <c:axId val="89121999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,7 +2683,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34139189"/>
+        <c:crossAx val="93862686"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2737,7 +2737,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2915,11 +2915,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="50367396"/>
-        <c:axId val="3793270"/>
+        <c:axId val="90707008"/>
+        <c:axId val="89598582"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="50367396"/>
+        <c:axId val="90707008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,14 +2962,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3793270"/>
+        <c:crossAx val="89598582"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3793270"/>
+        <c:axId val="89598582"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,7 +3012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50367396"/>
+        <c:crossAx val="90707008"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -3077,9 +3077,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1443960</xdr:colOff>
+      <xdr:colOff>1443600</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>54000</xdr:rowOff>
+      <xdr:rowOff>53640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3093,7 +3093,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4629960" y="9009720"/>
-          <a:ext cx="18283680" cy="3294000"/>
+          <a:ext cx="18283320" cy="3293640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3114,9 +3114,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1470960</xdr:colOff>
+      <xdr:colOff>1470600</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>58320</xdr:rowOff>
+      <xdr:rowOff>57960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3130,7 +3130,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4642560" y="4957560"/>
-          <a:ext cx="18298080" cy="3365640"/>
+          <a:ext cx="18297720" cy="3365280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3151,9 +3151,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1469880</xdr:colOff>
+      <xdr:colOff>1469520</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>91800</xdr:rowOff>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3167,7 +3167,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4670640" y="12968640"/>
-          <a:ext cx="18268920" cy="3002400"/>
+          <a:ext cx="18268560" cy="3002040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3188,9 +3188,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>14760</xdr:colOff>
+      <xdr:colOff>14400</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>86400</xdr:rowOff>
+      <xdr:rowOff>86040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3204,7 +3204,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4658040" y="16432200"/>
-          <a:ext cx="18303480" cy="3685680"/>
+          <a:ext cx="18303120" cy="3685320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3225,9 +3225,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1451160</xdr:colOff>
+      <xdr:colOff>1450800</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>40680</xdr:rowOff>
+      <xdr:rowOff>40320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3241,7 +3241,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4695480" y="20664360"/>
-          <a:ext cx="18225360" cy="4129560"/>
+          <a:ext cx="18225000" cy="4129200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3262,9 +3262,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1462680</xdr:colOff>
+      <xdr:colOff>1462320</xdr:colOff>
       <xdr:row>102</xdr:row>
-      <xdr:rowOff>73800</xdr:rowOff>
+      <xdr:rowOff>73440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3278,7 +3278,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4667400" y="25785720"/>
-          <a:ext cx="18264960" cy="4131720"/>
+          <a:ext cx="18264600" cy="4131360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3299,9 +3299,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1473120</xdr:colOff>
+      <xdr:colOff>1472760</xdr:colOff>
       <xdr:row>104</xdr:row>
-      <xdr:rowOff>4334040</xdr:rowOff>
+      <xdr:rowOff>4333680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3315,7 +3315,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4668120" y="30150360"/>
-          <a:ext cx="18274680" cy="4408200"/>
+          <a:ext cx="18274320" cy="4407840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3336,9 +3336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1452960</xdr:colOff>
+      <xdr:colOff>1452600</xdr:colOff>
       <xdr:row>126</xdr:row>
-      <xdr:rowOff>12600</xdr:rowOff>
+      <xdr:rowOff>12240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3352,7 +3352,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4667400" y="35050320"/>
-          <a:ext cx="18255240" cy="6337440"/>
+          <a:ext cx="18254880" cy="6337080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3373,9 +3373,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1463040</xdr:colOff>
+      <xdr:colOff>1462680</xdr:colOff>
       <xdr:row>145</xdr:row>
-      <xdr:rowOff>150840</xdr:rowOff>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3389,7 +3389,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4667760" y="42155280"/>
-          <a:ext cx="18264960" cy="4971240"/>
+          <a:ext cx="18264600" cy="4970880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3410,9 +3410,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1423440</xdr:colOff>
+      <xdr:colOff>1423080</xdr:colOff>
       <xdr:row>160</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
+      <xdr:rowOff>30240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3426,44 +3426,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4628160" y="47598120"/>
-          <a:ext cx="18264960" cy="4958280"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1337760</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>102240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1387080</xdr:colOff>
-      <xdr:row>176</xdr:row>
-      <xdr:rowOff>101160</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Imagen 11" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4601520" y="53008920"/>
-          <a:ext cx="18255240" cy="3908160"/>
+          <a:ext cx="18264600" cy="4957920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3479,18 +3442,55 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>1377360</xdr:colOff>
-      <xdr:row>180</xdr:row>
-      <xdr:rowOff>38520</xdr:rowOff>
+      <xdr:row>179</xdr:row>
+      <xdr:rowOff>89280</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1446120</xdr:colOff>
-      <xdr:row>192</xdr:row>
-      <xdr:rowOff>32400</xdr:rowOff>
+      <xdr:colOff>1445760</xdr:colOff>
+      <xdr:row>191</xdr:row>
+      <xdr:rowOff>55080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Imagen 12" descr=""/>
+        <xdr:cNvPr id="10" name="Imagen 12" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4641120" y="57560400"/>
+          <a:ext cx="18274320" cy="3869640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1351800</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>76680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1263240</xdr:colOff>
+      <xdr:row>174</xdr:row>
+      <xdr:rowOff>89280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 11" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -3499,8 +3499,82 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4641120" y="57560400"/>
-          <a:ext cx="18274680" cy="3870000"/>
+          <a:off x="4615560" y="52983360"/>
+          <a:ext cx="18117360" cy="3736440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1358280</xdr:colOff>
+      <xdr:row>193</xdr:row>
+      <xdr:rowOff>37080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1446840</xdr:colOff>
+      <xdr:row>208</xdr:row>
+      <xdr:rowOff>69840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 13" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4622040" y="61765200"/>
+          <a:ext cx="18294480" cy="3936960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1411200</xdr:colOff>
+      <xdr:row>215</xdr:row>
+      <xdr:rowOff>99360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1470240</xdr:colOff>
+      <xdr:row>222</xdr:row>
+      <xdr:rowOff>93960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 14" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4674960" y="66925440"/>
+          <a:ext cx="18264960" cy="3908520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3526,18 +3600,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>756720</xdr:colOff>
+      <xdr:colOff>756360</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>130680</xdr:rowOff>
+      <xdr:rowOff>130320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Chart"/>
+        <xdr:cNvPr id="14" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9531000" y="380880"/>
-        <a:ext cx="4912920" cy="3046680"/>
+        <a:ext cx="4912560" cy="3046320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3556,18 +3630,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>756720</xdr:colOff>
+      <xdr:colOff>756360</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>5760</xdr:rowOff>
+      <xdr:rowOff>5400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="13" name="Chart"/>
+        <xdr:cNvPr id="15" name="Chart"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9531000" y="3619080"/>
-        <a:ext cx="4912920" cy="3998880"/>
+        <a:ext cx="4912560" cy="3998520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -6393,7 +6467,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M222"/>
+  <dimension ref="A1:M244"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
@@ -7322,7 +7396,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="137" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="148" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="14" t="s">
         <v>368</v>
       </c>
@@ -7369,63 +7443,129 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="193" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B200" s="14" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="272" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B204" s="14" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="306" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B209" s="14" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="214" customFormat="false" ht="261" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B214" s="14" t="s">
-        <v>374</v>
-      </c>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B196" s="14"/>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B197" s="14"/>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B198" s="14"/>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B199" s="14"/>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B200" s="14"/>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B201" s="14"/>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B202" s="14"/>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B203" s="14"/>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B204" s="14"/>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B205" s="14"/>
+    </row>
+    <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B206" s="14"/>
+    </row>
+    <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B207" s="14"/>
+    </row>
+    <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B208" s="14"/>
+    </row>
+    <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B209" s="14"/>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B210" s="14"/>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B211" s="14"/>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B212" s="14"/>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B213" s="14"/>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="227" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B218" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B219" s="14"/>
+    </row>
+    <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B220" s="14"/>
+    </row>
+    <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B221" s="14"/>
+    </row>
+    <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B222" s="14"/>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="272" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B226" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="306" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B231" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="261" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B236" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A239" s="1" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="250" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B218" s="14" t="s">
+    <row r="240" customFormat="false" ht="250" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B240" s="14" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1" t="s">
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A243" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B222" s="14" t="s">
+    <row r="244" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B244" s="14" t="s">
         <v>376</v>
       </c>
     </row>
@@ -7921,7 +8061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7BEF86E0-B0F1-4488-A046-EA5776225150}</x14:id>
+          <x14:id>{D34B7274-F94E-4A76-BEA8-C031F8237B2A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -7943,7 +8083,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7BEF86E0-B0F1-4488-A046-EA5776225150}">
+          <x14:cfRule type="dataBar" id="{D34B7274-F94E-4A76-BEA8-C031F8237B2A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8576,7 +8716,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{AB97E071-6A1C-4AC9-8A93-9377AF9A10B0}</x14:id>
+          <x14:id>{EBDD3CC4-CF50-4749-AAE0-A41E449E6AD5}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8593,7 +8733,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{AB97E071-6A1C-4AC9-8A93-9377AF9A10B0}">
+          <x14:cfRule type="dataBar" id="{EBDD3CC4-CF50-4749-AAE0-A41E449E6AD5}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -9032,7 +9172,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{FA31307F-9FC6-4540-9BEB-DB8960F87D1C}</x14:id>
+          <x14:id>{89C38499-92D2-4959-9C19-A4C0FB90508A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9057,7 +9197,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{FA31307F-9FC6-4540-9BEB-DB8960F87D1C}">
+          <x14:cfRule type="dataBar" id="{89C38499-92D2-4959-9C19-A4C0FB90508A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -2456,7 +2456,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2586,11 +2586,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93862686"/>
-        <c:axId val="89121999"/>
+        <c:axId val="20156672"/>
+        <c:axId val="77796890"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93862686"/>
+        <c:axId val="20156672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2633,14 +2633,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89121999"/>
+        <c:crossAx val="77796890"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89121999"/>
+        <c:axId val="77796890"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,7 +2683,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93862686"/>
+        <c:crossAx val="20156672"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2737,7 +2737,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2915,11 +2915,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="90707008"/>
-        <c:axId val="89598582"/>
+        <c:axId val="92808703"/>
+        <c:axId val="55203752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="90707008"/>
+        <c:axId val="92808703"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,14 +2962,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89598582"/>
+        <c:crossAx val="55203752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="89598582"/>
+        <c:axId val="55203752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,7 +3012,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90707008"/>
+        <c:crossAx val="92808703"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -8061,7 +8061,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D34B7274-F94E-4A76-BEA8-C031F8237B2A}</x14:id>
+          <x14:id>{3ABEB029-9772-4E6D-AEEC-5FBFE2973957}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8083,7 +8083,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D34B7274-F94E-4A76-BEA8-C031F8237B2A}">
+          <x14:cfRule type="dataBar" id="{3ABEB029-9772-4E6D-AEEC-5FBFE2973957}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8716,7 +8716,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EBDD3CC4-CF50-4749-AAE0-A41E449E6AD5}</x14:id>
+          <x14:id>{B9CF78B3-4E70-49BA-8F6D-B4B6B091ACE8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8733,7 +8733,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EBDD3CC4-CF50-4749-AAE0-A41E449E6AD5}">
+          <x14:cfRule type="dataBar" id="{B9CF78B3-4E70-49BA-8F6D-B4B6B091ACE8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -9172,7 +9172,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{89C38499-92D2-4959-9C19-A4C0FB90508A}</x14:id>
+          <x14:id>{D5915D34-A471-486B-88D6-11BA2740B2AC}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9197,7 +9197,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{89C38499-92D2-4959-9C19-A4C0FB90508A}">
+          <x14:cfRule type="dataBar" id="{D5915D34-A471-486B-88D6-11BA2740B2AC}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>

--- a/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
+++ b/RVI20U32/Docs/Plantilla_Verificacion_RV32I_5Etapas_IF_BRAM.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="620">
   <si>
     <t xml:space="preserve">Plantilla de verificación RV32I para core pipeline de 5 etapas con IF de 2 ciclos (BRAM síncrona)</t>
   </si>
@@ -1411,6 +1411,22 @@
     addi x9, x0, 99          # wrong-path
 target:
     addi x11, x0, 11
+done:
+    jal x0, done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-020 (EXTRA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.section .text.start
+.globl _start
+_start:
+    addi x1, x0, 5
+    lw   x2, 0(x1)      # load (provoca hazard)
+    beq  x2, x2, target
+    addi x3, x0, 99     # wrong path
+target:
+    addi x4, x0, 42
 done:
     jal x0, done</t>
   </si>
@@ -2456,7 +2472,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2586,11 +2602,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="20156672"/>
-        <c:axId val="77796890"/>
+        <c:axId val="78775798"/>
+        <c:axId val="59007847"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20156672"/>
+        <c:axId val="78775798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2633,14 +2649,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77796890"/>
+        <c:crossAx val="59007847"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77796890"/>
+        <c:axId val="59007847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2683,7 +2699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20156672"/>
+        <c:crossAx val="78775798"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -2737,7 +2753,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
@@ -2915,11 +2931,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="92808703"/>
-        <c:axId val="55203752"/>
+        <c:axId val="65383091"/>
+        <c:axId val="16826754"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92808703"/>
+        <c:axId val="65383091"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2962,14 +2978,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55203752"/>
+        <c:crossAx val="16826754"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55203752"/>
+        <c:axId val="16826754"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3012,7 +3028,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92808703"/>
+        <c:crossAx val="65383091"/>
         <c:crosses val="autoZero"/>
       </c:valAx>
       <c:spPr>
@@ -3956,7 +3972,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>226</v>
@@ -3965,22 +3981,22 @@
         <v>222</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="J1" s="3" t="s">
         <v>225</v>
@@ -3994,34 +4010,34 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>311</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>238</v>
@@ -4032,34 +4048,34 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>311</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>104</v>
@@ -4070,34 +4086,34 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>317</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>238</v>
@@ -4108,34 +4124,34 @@
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>254</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>238</v>
@@ -4146,34 +4162,34 @@
     </row>
     <row r="6" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>104</v>
@@ -4184,34 +4200,34 @@
     </row>
     <row r="7" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>104</v>
@@ -4222,22 +4238,22 @@
     </row>
     <row r="8" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>230</v>
@@ -4246,10 +4262,10 @@
         <v>254</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>238</v>
@@ -4260,34 +4276,34 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>166</v>
@@ -6467,7 +6483,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M244"/>
+  <dimension ref="A1:M249"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.36"/>
@@ -7567,6 +7583,16 @@
     <row r="244" customFormat="false" ht="340" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B244" s="14" t="s">
         <v>376</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A248" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="171" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B249" s="14" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -7639,22 +7665,22 @@
         <v>220</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>33</v>
@@ -7665,7 +7691,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -7687,7 +7713,7 @@
         <v>254</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
@@ -7709,7 +7735,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
@@ -7731,7 +7757,7 @@
         <v>273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
@@ -7753,7 +7779,7 @@
         <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
@@ -7772,10 +7798,10 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>1</v>
@@ -7794,10 +7820,10 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>3</v>
@@ -7816,10 +7842,10 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>4</v>
@@ -7838,10 +7864,10 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>4</v>
@@ -7860,10 +7886,10 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>1</v>
@@ -7882,10 +7908,10 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>3</v>
@@ -7907,7 +7933,7 @@
         <v>335</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>2</v>
@@ -7926,10 +7952,10 @@
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>1</v>
@@ -7948,10 +7974,10 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>2</v>
@@ -7970,10 +7996,10 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
@@ -7985,17 +8011,17 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
@@ -8007,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
@@ -8017,7 +8043,7 @@
         <v>349</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>2</v>
@@ -8061,7 +8087,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3ABEB029-9772-4E6D-AEEC-5FBFE2973957}</x14:id>
+          <x14:id>{1A8769EC-F920-4DB0-9178-A646C47717F8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8083,7 +8109,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3ABEB029-9772-4E6D-AEEC-5FBFE2973957}">
+          <x14:cfRule type="dataBar" id="{1A8769EC-F920-4DB0-9178-A646C47717F8}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8119,28 +8145,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="3"/>
@@ -8167,10 +8193,10 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -8187,7 +8213,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">COUNTA(Matriz_RV32I!B2:B100)</f>
@@ -8208,7 +8234,7 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Completado")</f>
@@ -8229,7 +8255,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
@@ -8250,7 +8276,7 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B7" s="16" t="n">
         <f aca="false">IFERROR(COUNTIF(Cobertura_Modulos!F2:F100,"Completado")/COUNTIF(Cobertura_Modulos!F2:F100,"&lt;&gt;N/A"),0)</f>
@@ -8271,7 +8297,7 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">COUNTIF(Hazards_Forwarding!L2:L100,"Completado")</f>
@@ -8292,7 +8318,7 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">COUNTIF(Escenarios_Prueba!J2:J120,"Completado")</f>
@@ -8316,17 +8342,17 @@
         <v>92</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -8368,7 +8394,7 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"En progreso")</f>
@@ -8397,7 +8423,7 @@
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"Bloqueado")</f>
@@ -8455,7 +8481,7 @@
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">COUNTIF(Matriz_RV32I!K2:K100,"N/A")</f>
@@ -8484,14 +8510,14 @@
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D16,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8512,7 +8538,7 @@
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">COUNTIF(Documentos_Entradas!D2:D100,"Sí")</f>
@@ -8520,7 +8546,7 @@
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D17,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8541,7 +8567,7 @@
     </row>
     <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B18" s="4" t="n">
         <f aca="false">COUNTIFS(Documentos_Entradas!D2:D100,"Sí",Documentos_Entradas!I2:I100,"Completo")</f>
@@ -8549,7 +8575,7 @@
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D18,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8570,7 +8596,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">COUNTA(MMIO_Interrupts_Traps!A2:A100)</f>
@@ -8578,7 +8604,7 @@
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D19,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8599,7 +8625,7 @@
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B20" s="3" t="n">
         <f aca="false">COUNTIF(MMIO_Interrupts_Traps!J2:J100,"Completado")</f>
@@ -8607,7 +8633,7 @@
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D20,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8628,7 +8654,7 @@
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B21" s="16" t="n">
         <f aca="false">IFERROR(B20/B19,0)</f>
@@ -8660,7 +8686,7 @@
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E22" s="16" t="n">
         <f aca="false">IFERROR(INDEX(Cobertura_Modulos!E:E,MATCH(D22,Cobertura_Modulos!A:A,0)),0)</f>
@@ -8716,7 +8742,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B9CF78B3-4E70-49BA-8F6D-B4B6B091ACE8}</x14:id>
+          <x14:id>{8A2E8F3C-4269-43ED-862C-873176729D92}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -8733,7 +8759,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B9CF78B3-4E70-49BA-8F6D-B4B6B091ACE8}">
+          <x14:cfRule type="dataBar" id="{8A2E8F3C-4269-43ED-862C-873176729D92}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8772,31 +8798,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>92</v>
@@ -8807,22 +8833,22 @@
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>4</v>
@@ -8841,22 +8867,22 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>8</v>
@@ -8875,22 +8901,22 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>4</v>
@@ -8909,22 +8935,22 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8</v>
@@ -8943,22 +8969,22 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>6</v>
@@ -8977,22 +9003,22 @@
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4</v>
@@ -9011,16 +9037,16 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>67</v>
@@ -9045,16 +9071,16 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>67</v>
@@ -9079,16 +9105,16 @@
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>67</v>
@@ -9113,16 +9139,16 @@
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>216</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>67</v>
@@ -9172,7 +9198,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D5915D34-A471-486B-88D6-11BA2740B2AC}</x14:id>
+          <x14:id>{92002061-B464-4800-A34C-B18D962352D7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -9197,7 +9223,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D5915D34-A471-486B-88D6-11BA2740B2AC}">
+          <x14:cfRule type="dataBar" id="{92002061-B464-4800-A34C-B18D962352D7}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -9233,10 +9259,10 @@
         <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9255,13 +9281,13 @@
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>38</v>
@@ -9269,7 +9295,7 @@
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>212</v>
@@ -9278,7 +9304,7 @@
         <v>350</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9295,7 +9321,7 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
@@ -9307,7 +9333,7 @@
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D7" s="3"/>
     </row>
@@ -9355,25 +9381,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>349</v>
@@ -9382,7 +9408,7 @@
         <v>92</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>33</v>
@@ -9391,62 +9417,62 @@
     </row>
     <row r="2" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>102</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>102</v>
@@ -9457,28 +9483,28 @@
     </row>
     <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>102</v>
@@ -9489,25 +9515,25 @@
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>140</v>
@@ -9521,28 +9547,28 @@
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>102</v>
@@ -9556,25 +9582,25 @@
         <v>254</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>102</v>
@@ -9585,28 +9611,28 @@
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>102</v>
@@ -9617,28 +9643,28 @@
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>102</v>
@@ -9652,25 +9678,25 @@
         <v>335</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>102</v>
@@ -9684,25 +9710,25 @@
         <v>342</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>102</v>
@@ -9713,35 +9739,35 @@
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L12" s="3"/>
     </row>
